--- a/TeacherTraining/templates/master-availability-template.xlsx
+++ b/TeacherTraining/templates/master-availability-template.xlsx
@@ -35,12 +35,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-10</t>
+          <t xml:space="preserve">2026-11-15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
     </row>
